--- a/data_static/balneabilidade/balneabilidade.xlsx
+++ b/data_static/balneabilidade/balneabilidade.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c476c95a5a05174c/OD/LOFEC - TAPIOCA/RCP/Aditivo/Praia segura/APP/praia_segura/data_static/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\praia_segura_backend\data_static\balneabilidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="11_F25DC773A252ABDACC10487E89DF624C5BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0F4AB1A-BB4C-495D-9321-52E62BF40D16}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F236836-74F5-4DE7-A7AC-F36EDCFA2B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1635" yWindow="2280" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
-    <t>COD_CPRH</t>
-  </si>
-  <si>
     <t>LOCAL</t>
   </si>
   <si>
@@ -91,6 +88,9 @@
   </si>
   <si>
     <t xml:space="preserve">Própria </t>
+  </si>
+  <si>
+    <t>COD_CPRH_BALNEABILIDADE</t>
   </si>
 </sst>
 </file>
@@ -419,33 +419,33 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>-8.0911150000000003</v>
@@ -454,21 +454,21 @@
         <v>-34.881484999999998</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>-8.1153969999999997</v>
@@ -477,21 +477,21 @@
         <v>-34.891800000000003</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>-8.1496600000000008</v>
@@ -500,21 +500,21 @@
         <v>-34.906945</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5">
         <v>-8.1568679999999993</v>
@@ -523,13 +523,13 @@
         <v>-34.909658</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
